--- a/05_statistics/pathway_frequency_summary.xlsx
+++ b/05_statistics/pathway_frequency_summary.xlsx
@@ -477,25 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="3">
@@ -505,25 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="4">
@@ -533,25 +533,25 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -573,13 +573,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="6">
@@ -589,25 +589,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="7">
@@ -620,22 +620,22 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
   </sheetData>

--- a/05_statistics/pathway_frequency_summary.xlsx
+++ b/05_statistics/pathway_frequency_summary.xlsx
@@ -508,7 +508,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -523,7 +523,7 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -551,7 +551,7 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -598,13 +598,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="H6" t="n">
         <v>0.1538461538461539</v>
